--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/02_CMP2 - Risk, İş Sürekliliği ve Bilgi Sistemleri/EKG-YNT-FRM-05_periyodik_is_surekliligi_risk_gozden_gecirme_ve_aksiyon.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/02_CMP2 - Risk, İş Sürekliliği ve Bilgi Sistemleri/EKG-YNT-FRM-05_periyodik_is_surekliligi_risk_gozden_gecirme_ve_aksiyon.xlsx
@@ -993,7 +993,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-FRM-05&amp;C&amp;"Arial,Regular"&amp;11Periyodik İş Sürekliliği Risk Gözden Geçirme ve Aksiyon Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc18fa71801945af"/>
   <x:tableParts count="1">
@@ -1341,7 +1342,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-FRM-05&amp;C&amp;"Arial,Regular"&amp;11Periyodik İş Sürekliliği Risk Gözden Geçirme ve Aksiyon Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0db39a2e4a14e09"/>
   <x:tableParts count="1">
